--- a/Table_S4.xlsx
+++ b/Table_S4.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4A_primary_0p85" sheetId="1" r:id="R5c1ffdbe1ece46c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4B_all_thresholds" sheetId="2" r:id="R4643fc4a1f644155"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4C_GC_correlation" sheetId="3" r:id="R5a303394c7474bfb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4D_design_QC" sheetId="4" r:id="Re0a14a1ff23a4494"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4A_primary_0p85" sheetId="1" r:id="R75fb862755654622"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4B_all_thresholds" sheetId="2" r:id="R9f50a13dbb6b459a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4C_GC_correlation" sheetId="3" r:id="R869e542fcc1a4db2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4D_design_QC" sheetId="4" r:id="R6c7c6c93f8874950"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -44,7 +44,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -57,6 +57,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -176,9 +182,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -308,76 +314,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="14.399999618530273"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="90" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
         <x:v>Table S4. Constrained-mutant sensitivity and exact-GC control for the in-silico-designed 49-bp ONSEN HSE-disrupted sequence.</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="n"/>
-      <x:c r="C1" s="1" t="n"/>
-      <x:c r="D1" s="1" t="n"/>
-      <x:c r="E1" s="1" t="n"/>
-      <x:c r="F1" s="1" t="n"/>
-      <x:c r="G1" s="1" t="n"/>
-      <x:c r="H1" s="1" t="n"/>
-      <x:c r="I1" s="1" t="n"/>
+      <x:c r="B1" s="7" t="n"/>
+      <x:c r="C1" s="7" t="n"/>
+      <x:c r="D1" s="7" t="n"/>
+      <x:c r="E1" s="7" t="n"/>
+      <x:c r="F1" s="7" t="n"/>
+      <x:c r="G1" s="7" t="n"/>
+      <x:c r="H1" s="7" t="n"/>
+      <x:c r="I1" s="7" t="n"/>
+      <x:c r="J1" s="8"/>
+      <x:c r="K1" s="8"/>
+      <x:c r="L1" s="8"/>
+      <x:c r="M1" s="8"/>
     </x:row>
     <x:row r="2"/>
-    <x:row r="3">
-      <x:c r="A3" t="inlineStr">
+    <x:row r="3" ht="36" customHeight="1">
+      <x:c r="A3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Comparison space</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" t="inlineStr">
+      <x:c r="B3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Relative PWM-score threshold</x:t>
         </x:is>
       </x:c>
-      <x:c r="C3" t="inlineStr">
+      <x:c r="C3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TF family</x:t>
         </x:is>
       </x:c>
-      <x:c r="D3" t="inlineStr">
+      <x:c r="D3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Number of comparator sequences</x:t>
         </x:is>
       </x:c>
-      <x:c r="E3" t="str">
+      <x:c r="E3" s="8" t="str">
         <x:v>Designed-sequence motif-position hits</x:v>
       </x:c>
-      <x:c r="F3" t="inlineStr">
+      <x:c r="F3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Comparator 2.5th percentile</x:t>
         </x:is>
       </x:c>
-      <x:c r="G3" t="inlineStr">
+      <x:c r="G3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Comparator median</x:t>
         </x:is>
       </x:c>
-      <x:c r="H3" t="inlineStr">
+      <x:c r="H3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Comparator 97.5th percentile</x:t>
         </x:is>
       </x:c>
-      <x:c r="I3" t="inlineStr">
+      <x:c r="I3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Comparator maximum</x:t>
         </x:is>
       </x:c>
-      <x:c r="J3" t="inlineStr">
+      <x:c r="J3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Empirical midrank percentile (%)</x:t>
         </x:is>
       </x:c>
-      <x:c r="K3" t="inlineStr">
+      <x:c r="K3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Empirical upper-tail P</x:t>
         </x:is>
       </x:c>
-      <x:c r="L3" t="inlineStr">
+      <x:c r="L3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Empirical lower-tail P</x:t>
         </x:is>
@@ -388,8 +413,8 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="inlineStr">
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -433,8 +458,8 @@
         <x:v>No HSF-family motif-position hits were detected in the designed sequence; the comparator distribution was also concentrated at or near zero.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="inlineStr">
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -478,8 +503,8 @@
         <x:v>The designed sequence was in the upper tail of this comparator distribution.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="inlineStr">
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -523,8 +548,8 @@
         <x:v>The designed-sequence value was below the comparator median but was not statistically exceptional in the corresponding empirical tail test.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="inlineStr">
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -537,6 +562,9 @@
           <x:t xml:space="preserve">HSF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D7" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E7" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -565,8 +593,8 @@
         <x:v>No HSF-family motif-position hits were detected in the designed sequence; HSF loss was also retained across the valid exact-GC constrained designs.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="inlineStr">
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -579,6 +607,9 @@
           <x:t xml:space="preserve">AP2/ERF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D8" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E8" t="n">
         <x:v>61</x:v>
       </x:c>
@@ -607,8 +638,8 @@
         <x:v>The designed-sequence value exceeded the comparator median but was not statistically exceptional in the corresponding empirical tail test.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="inlineStr">
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -621,6 +652,9 @@
           <x:t xml:space="preserve">DOF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D9" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E9" t="n">
         <x:v>33</x:v>
       </x:c>
@@ -650,6 +684,9 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:M1"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -657,68 +694,95 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="14.399999618530273"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="90" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
         <x:v>Table S4. Constrained-mutant sensitivity and exact-GC control for the in-silico-designed 49-bp ONSEN HSE-disrupted sequence.</x:v>
       </x:c>
+      <x:c r="B1" s="8"/>
+      <x:c r="C1" s="8"/>
+      <x:c r="D1" s="8"/>
+      <x:c r="E1" s="8"/>
+      <x:c r="F1" s="8"/>
+      <x:c r="G1" s="8"/>
+      <x:c r="H1" s="8"/>
+      <x:c r="I1" s="8"/>
+      <x:c r="J1" s="8"/>
+      <x:c r="K1" s="8"/>
+      <x:c r="L1" s="8"/>
+      <x:c r="M1" s="8"/>
     </x:row>
     <x:row r="2"/>
-    <x:row r="3">
-      <x:c r="A3" t="inlineStr">
+    <x:row r="3" ht="36" customHeight="1">
+      <x:c r="A3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Comparison space</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" t="inlineStr">
+      <x:c r="B3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Relative PWM-score threshold</x:t>
         </x:is>
       </x:c>
-      <x:c r="C3" t="inlineStr">
+      <x:c r="C3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TF family</x:t>
         </x:is>
       </x:c>
-      <x:c r="D3" t="inlineStr">
+      <x:c r="D3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Number of comparator sequences</x:t>
         </x:is>
       </x:c>
-      <x:c r="E3" t="str">
+      <x:c r="E3" s="8" t="str">
         <x:v>Designed-sequence motif-position hits</x:v>
       </x:c>
-      <x:c r="F3" t="inlineStr">
+      <x:c r="F3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Comparator 2.5th percentile</x:t>
         </x:is>
       </x:c>
-      <x:c r="G3" t="inlineStr">
+      <x:c r="G3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Comparator median</x:t>
         </x:is>
       </x:c>
-      <x:c r="H3" t="inlineStr">
+      <x:c r="H3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Comparator 97.5th percentile</x:t>
         </x:is>
       </x:c>
-      <x:c r="I3" t="inlineStr">
+      <x:c r="I3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Comparator maximum</x:t>
         </x:is>
       </x:c>
-      <x:c r="J3" t="inlineStr">
+      <x:c r="J3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Empirical midrank percentile (%)</x:t>
         </x:is>
       </x:c>
-      <x:c r="K3" t="inlineStr">
+      <x:c r="K3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Empirical upper-tail P</x:t>
         </x:is>
       </x:c>
-      <x:c r="L3" t="inlineStr">
+      <x:c r="L3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Empirical lower-tail P</x:t>
         </x:is>
@@ -729,8 +793,8 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="inlineStr">
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -774,8 +838,8 @@
         <x:v>No HSF-family motif-position hits were detected in the designed sequence; the comparator distribution was also concentrated at or near zero.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="inlineStr">
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -819,8 +883,8 @@
         <x:v>The designed sequence was in the upper tail of this comparator distribution.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="inlineStr">
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -864,8 +928,8 @@
         <x:v>The designed-sequence value was below the comparator median but was not statistically exceptional in the corresponding empirical tail test.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="inlineStr">
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -909,8 +973,8 @@
         <x:v>No HSF-family motif-position hits were detected in the designed sequence; the comparator distribution was also concentrated at or near zero.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="inlineStr">
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -954,8 +1018,8 @@
         <x:v>The designed sequence was in the upper tail of this comparator distribution.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="inlineStr">
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -999,8 +1063,8 @@
         <x:v>The designed-sequence value was below the comparator median but was not statistically exceptional in the corresponding empirical tail test.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="inlineStr">
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -1044,8 +1108,8 @@
         <x:v>No HSF-family motif-position hits were detected in the designed sequence; the comparator distribution was also concentrated at or near zero.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="inlineStr">
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -1089,8 +1153,8 @@
         <x:v>The designed sequence was in the upper tail of this comparator distribution.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="inlineStr">
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -1134,8 +1198,8 @@
         <x:v>The designed-sequence value was not statistically exceptional within this comparator distribution.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="inlineStr">
+    <x:row r="13" ht="36" customHeight="1">
+      <x:c r="A13" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -1179,8 +1243,8 @@
         <x:v>No HSF-family motif-position hits were detected in the designed sequence; the comparator distribution was also concentrated at or near zero.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="inlineStr">
+    <x:row r="14" ht="36" customHeight="1">
+      <x:c r="A14" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -1224,8 +1288,8 @@
         <x:v>The designed sequence was in the upper tail of this comparator distribution.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="inlineStr">
+    <x:row r="15" ht="36" customHeight="1">
+      <x:c r="A15" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Constrained random mutants with variable GC content</x:t>
         </x:is>
@@ -1269,8 +1333,8 @@
         <x:v>The designed-sequence value was not statistically exceptional within this comparator distribution.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="inlineStr">
+    <x:row r="16" ht="36" customHeight="1">
+      <x:c r="A16" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -1283,6 +1347,9 @@
           <x:t xml:space="preserve">HSF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D16" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1311,8 +1378,8 @@
         <x:v>No HSF-family motif-position hits were detected in the designed sequence; HSF loss was also retained across the valid exact-GC constrained designs.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="inlineStr">
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -1325,6 +1392,9 @@
           <x:t xml:space="preserve">AP2/ERF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D17" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E17" t="n">
         <x:v>121</x:v>
       </x:c>
@@ -1353,8 +1423,8 @@
         <x:v>The designed-sequence value exceeded the comparator median but was not statistically exceptional in the corresponding empirical tail test.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="inlineStr">
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -1367,6 +1437,9 @@
           <x:t xml:space="preserve">DOF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D18" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E18" t="n">
         <x:v>65</x:v>
       </x:c>
@@ -1395,8 +1468,8 @@
         <x:v>The designed-sequence value exceeded the comparator median but was not statistically exceptional in the corresponding empirical tail test.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="inlineStr">
+    <x:row r="19" ht="36" customHeight="1">
+      <x:c r="A19" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -1409,6 +1482,9 @@
           <x:t xml:space="preserve">HSF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D19" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E19" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1437,8 +1513,8 @@
         <x:v>No HSF-family motif-position hits were detected in the designed sequence; HSF loss was also retained across the valid exact-GC constrained designs.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="inlineStr">
+    <x:row r="20" ht="36" customHeight="1">
+      <x:c r="A20" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -1451,6 +1527,9 @@
           <x:t xml:space="preserve">AP2/ERF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D20" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E20" t="n">
         <x:v>61</x:v>
       </x:c>
@@ -1479,8 +1558,8 @@
         <x:v>The designed-sequence value exceeded the comparator median but was not statistically exceptional in the corresponding empirical tail test.</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="inlineStr">
+    <x:row r="21" ht="36" customHeight="1">
+      <x:c r="A21" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -1493,6 +1572,9 @@
           <x:t xml:space="preserve">DOF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D21" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E21" t="n">
         <x:v>33</x:v>
       </x:c>
@@ -1521,8 +1603,8 @@
         <x:v>The designed-sequence value was below the comparator median but was not statistically exceptional in the corresponding empirical tail test.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="inlineStr">
+    <x:row r="22" ht="36" customHeight="1">
+      <x:c r="A22" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -1535,6 +1617,9 @@
           <x:t xml:space="preserve">HSF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D22" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E22" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1563,8 +1648,8 @@
         <x:v>No HSF-family motif-position hits were detected in the designed sequence; HSF loss was also retained across the valid exact-GC constrained designs.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="inlineStr">
+    <x:row r="23" ht="36" customHeight="1">
+      <x:c r="A23" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -1577,6 +1662,9 @@
           <x:t xml:space="preserve">AP2/ERF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D23" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E23" t="n">
         <x:v>14</x:v>
       </x:c>
@@ -1605,8 +1693,8 @@
         <x:v>The designed-sequence value exceeded the comparator median but was not statistically exceptional in the corresponding empirical tail test.</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="inlineStr">
+    <x:row r="24" ht="36" customHeight="1">
+      <x:c r="A24" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -1619,6 +1707,9 @@
           <x:t xml:space="preserve">DOF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D24" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E24" t="n">
         <x:v>12</x:v>
       </x:c>
@@ -1647,8 +1738,8 @@
         <x:v>The designed-sequence value was not statistically exceptional within this comparator distribution.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="inlineStr">
+    <x:row r="25" ht="36" customHeight="1">
+      <x:c r="A25" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -1661,6 +1752,9 @@
           <x:t xml:space="preserve">HSF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D25" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E25" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1689,8 +1783,8 @@
         <x:v>No HSF-family motif-position hits were detected in the designed sequence; HSF loss was also retained across the valid exact-GC constrained designs.</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="inlineStr">
+    <x:row r="26" ht="36" customHeight="1">
+      <x:c r="A26" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -1703,6 +1797,9 @@
           <x:t xml:space="preserve">AP2/ERF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D26" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E26" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -1731,8 +1828,8 @@
         <x:v>The designed-sequence value exceeded the comparator median but was not statistically exceptional in the corresponding empirical tail test.</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="inlineStr">
+    <x:row r="27" ht="36" customHeight="1">
+      <x:c r="A27" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Complete exact-GC constrained design space</x:t>
         </x:is>
@@ -1745,6 +1842,9 @@
           <x:t xml:space="preserve">DOF</x:t>
         </x:is>
       </x:c>
+      <x:c r="D27" t="n">
+        <x:v>5119</x:v>
+      </x:c>
       <x:c r="E27" t="n">
         <x:v>10</x:v>
       </x:c>
@@ -1774,6 +1874,9 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:M1"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -1781,50 +1884,67 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="14.399999618530273"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="70" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="6" t="str">
         <x:v>Table S4. Constrained-mutant sensitivity and exact-GC control for the in-silico-designed 49-bp ONSEN HSE-disrupted sequence.</x:v>
       </x:c>
+      <x:c r="B1" s="8"/>
+      <x:c r="C1" s="8"/>
+      <x:c r="D1" s="8"/>
+      <x:c r="E1" s="8"/>
+      <x:c r="F1" s="8"/>
+      <x:c r="G1" s="8"/>
+      <x:c r="H1" s="8"/>
     </x:row>
     <x:row r="2"/>
-    <x:row r="3">
-      <x:c r="A3" t="inlineStr">
+    <x:row r="3" ht="36" customHeight="1">
+      <x:c r="A3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Relative PWM-score threshold</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" t="inlineStr">
+      <x:c r="B3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TF family</x:t>
         </x:is>
       </x:c>
-      <x:c r="C3" t="inlineStr">
+      <x:c r="C3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Number of random mutants</x:t>
         </x:is>
       </x:c>
-      <x:c r="D3" t="inlineStr">
+      <x:c r="D3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Spearman rho</x:t>
         </x:is>
       </x:c>
-      <x:c r="E3" t="inlineStr">
+      <x:c r="E3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">P value (numeric)</x:t>
         </x:is>
       </x:c>
-      <x:c r="F3" t="inlineStr">
+      <x:c r="F3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">P value (display)</x:t>
         </x:is>
       </x:c>
-      <x:c r="G3" t="inlineStr">
+      <x:c r="G3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">P value exactly as stored in source CSV</x:t>
         </x:is>
       </x:c>
-      <x:c r="H3" t="inlineStr">
+      <x:c r="H3" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Status</x:t>
         </x:is>
@@ -2227,6 +2347,9 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -2234,11 +2357,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="14.399999618530273"/>
+  <x:cols>
+    <x:col min="1" max="1" width="35" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="65" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="90" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="72" customHeight="1">
       <x:c r="A1" s="6" t="str">
         <x:v>Table S4. Constrained-mutant sensitivity and exact-GC control for the in-silico-designed 49-bp ONSEN HSE-disrupted sequence.</x:v>
       </x:c>
+      <x:c r="B1" s="8"/>
+      <x:c r="C1" s="8"/>
     </x:row>
     <x:row r="2"/>
     <x:row r="3">
@@ -2580,6 +2710,9 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:C1"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>